--- a/data/teams/leagues/Averages_Finland_Veikkausliiga_2025.xlsx
+++ b/data/teams/leagues/Averages_Finland_Veikkausliiga_2025.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable" displayName="AveragesTable" ref="A1:EC14" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_Finland_Ve" displayName="AveragesTable_Finland_Ve" ref="A1:EC14" headerRowCount="1">
   <autoFilter ref="A1:EC14"/>
   <tableColumns count="133">
     <tableColumn id="1" name="team_name"/>

--- a/data/teams/leagues/Averages_Finland_Veikkausliiga_2025.xlsx
+++ b/data/teams/leagues/Averages_Finland_Veikkausliiga_2025.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_Finland_Ve" displayName="AveragesTable_Finland_Ve" ref="A1:EC14" headerRowCount="1">
-  <autoFilter ref="A1:EC14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_Finland_Ve" displayName="AveragesTable_Finland_Ve" ref="A1:EC13" headerRowCount="1">
+  <autoFilter ref="A1:EC13"/>
   <tableColumns count="133">
     <tableColumn id="1" name="team_name"/>
     <tableColumn id="2" name="total_games"/>
@@ -567,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EC14"/>
+  <dimension ref="A1:EC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.6" customWidth="1" min="1" max="1"/>
@@ -3789,262 +3789,262 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
+        <v>13</v>
+      </c>
+      <c r="D8" t="n">
         <v>14</v>
       </c>
-      <c r="D8" t="n">
-        <v>15</v>
-      </c>
       <c r="E8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H8" t="n">
+        <v>87.15000000000001</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="M8" t="n">
+        <v>57.08</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P8" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R8" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>49.54</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>17.38</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>80.20999999999999</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>38.93</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>11.07</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>45.29</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="F8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="H8" t="n">
-        <v>90.86</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5.93</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="M8" t="n">
-        <v>59.86</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="P8" t="n">
-        <v>12.14</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R8" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>50</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>12.79</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>8.859999999999999</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>16.07</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>80.59999999999999</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>10.93</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>5.53</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0.13</v>
-      </c>
       <c r="BA8" t="n">
-        <v>10.4</v>
+        <v>10.71</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.13</v>
+        <v>6.21</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.27</v>
+        <v>4.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>17.27</v>
+        <v>18.57</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.45</v>
+        <v>3.41</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.55</v>
+        <v>10.56</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.45</v>
+        <v>3.41</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="BN8" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.79</v>
+        <v>4.93</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.24</v>
+        <v>5.07</v>
       </c>
       <c r="BR8" t="n">
-        <v>93.09999999999999</v>
+        <v>92.59</v>
       </c>
       <c r="BS8" t="n">
-        <v>89.66</v>
+        <v>88.89</v>
       </c>
       <c r="BT8" t="n">
-        <v>79.31</v>
+        <v>77.78</v>
       </c>
       <c r="BU8" t="n">
-        <v>48.28</v>
+        <v>48.15</v>
       </c>
       <c r="BV8" t="n">
-        <v>34.48</v>
+        <v>33.33</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>62.07</v>
+        <v>62.96</v>
       </c>
       <c r="BY8" t="n">
-        <v>3.43</v>
+        <v>3.55</v>
       </c>
       <c r="BZ8" t="n">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="CA8" t="n">
-        <v>4.17</v>
+        <v>4.23</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.51</v>
+        <v>4.59</v>
       </c>
       <c r="CC8" t="n">
-        <v>5.28</v>
+        <v>5.49</v>
       </c>
       <c r="CD8" t="n">
-        <v>5.2</v>
+        <v>5.46</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.58</v>
@@ -4053,46 +4053,46 @@
         <v>1.34</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="CR8" t="n">
         <v>1.35</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="CU8" t="n">
         <v>1.69</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CX8" t="n">
         <v>1.5</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.47</v>
@@ -4101,88 +4101,88 @@
         <v>2.29</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.69</v>
+        <v>1.52</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="DH8" t="n">
-        <v>85.55</v>
+        <v>83.55</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.97</v>
+        <v>4.93</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="DM8" t="n">
-        <v>49.48</v>
+        <v>47.67</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.51</v>
+        <v>11.3</v>
       </c>
       <c r="DQ8" t="n">
-        <v>2.42</v>
+        <v>2.67</v>
       </c>
       <c r="DR8" t="n">
-        <v>4.65</v>
+        <v>5.08</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.45</v>
+        <v>0.19</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.45</v>
+        <v>0.19</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>47.31</v>
+        <v>47.34</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.55</v>
+        <v>11.66</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.45</v>
+        <v>7.48</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.11</v>
+        <v>4.19</v>
       </c>
       <c r="EA8" t="n">
-        <v>16.69</v>
+        <v>18</v>
       </c>
       <c r="EB8" t="n">
         <v>1.31</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="9">
@@ -5796,802 +5796,403 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="B13" t="n">
+        <v>27</v>
+      </c>
+      <c r="C13" t="n">
+        <v>14</v>
+      </c>
+      <c r="D13" t="n">
+        <v>13</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>93.79000000000001</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="K13" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M13" t="n">
+        <v>55.21</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="P13" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R13" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>51.21</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>21.64</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>84</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
         <v>2</v>
       </c>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>4</v>
-      </c>
-      <c r="H13" t="n">
-        <v>101</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>5</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>76</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1</v>
-      </c>
-      <c r="P13" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>62</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AD13" t="n">
+      <c r="AL13" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>39.92</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="AR13" t="n">
         <v>1.46</v>
       </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>94</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>-1</v>
-      </c>
       <c r="AS13" t="n">
-        <v>-1</v>
+        <v>5.38</v>
       </c>
       <c r="AT13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>45.69</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>18.92</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>88.89</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>81.48</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>59.26</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>89.08</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>47.85</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="DO13" t="n">
         <v>2</v>
       </c>
-      <c r="AU13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>30</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>44</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>4</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>4</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>3</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>100</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>100</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>100</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>50</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>50</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>50</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="CA13" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="CB13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="CC13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="CD13" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="CE13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="CF13" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="CG13" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="CH13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="CI13" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="CJ13" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="CK13" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="CL13" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="CM13" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="CN13" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="CO13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="CP13" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="CQ13" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="CS13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="CT13" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="CU13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="CV13" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="CW13" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="CX13" t="inlineStr"/>
-      <c r="CY13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="CZ13" t="inlineStr"/>
-      <c r="DA13" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="DB13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="DC13" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="DD13" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="DE13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG13" t="n">
-        <v>4</v>
-      </c>
-      <c r="DH13" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="DI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DK13" t="n">
-        <v>5</v>
-      </c>
-      <c r="DL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM13" t="n">
-        <v>60</v>
-      </c>
-      <c r="DN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO13" t="n">
-        <v>1</v>
-      </c>
       <c r="DP13" t="n">
-        <v>12</v>
+        <v>12.86</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-1</v>
+        <v>1.44</v>
       </c>
       <c r="DR13" t="n">
-        <v>-1</v>
+        <v>5.41</v>
       </c>
       <c r="DS13" t="n">
-        <v>15</v>
+        <v>0.11</v>
       </c>
       <c r="DT13" t="n">
-        <v>15</v>
+        <v>0.11</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>53</v>
+        <v>48.55</v>
       </c>
       <c r="DW13" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DX13" t="n">
-        <v>9</v>
+        <v>10.3</v>
       </c>
       <c r="DY13" t="n">
-        <v>4</v>
+        <v>6.48</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5</v>
+        <v>3.81</v>
       </c>
       <c r="EA13" t="n">
-        <v>-1</v>
+        <v>20.33</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>VPS</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>27</v>
-      </c>
-      <c r="C14" t="n">
-        <v>14</v>
-      </c>
-      <c r="D14" t="n">
-        <v>13</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H14" t="n">
-        <v>93.79000000000001</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="K14" t="n">
-        <v>6.93</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="M14" t="n">
-        <v>55.21</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="P14" t="n">
-        <v>12.86</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="R14" t="n">
-        <v>5.43</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>51.21</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>11.36</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>21.64</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>84</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>39.92</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>12.85</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>45.69</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>9.15</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>18.92</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>88.89</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>81.48</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>59.26</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>18.52</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>7.41</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="CB14" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="CC14" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="CD14" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="CE14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="CF14" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="CG14" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="CH14" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="CI14" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="CJ14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="CK14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="CL14" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="CM14" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="CN14" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="CO14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="CP14" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="CQ14" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="CR14" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="CS14" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="CT14" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="CU14" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="CV14" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="CW14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="CX14" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="CY14" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="CZ14" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="DA14" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="DB14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="DC14" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="DD14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="DE14" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DF14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DG14" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="DH14" t="n">
-        <v>89.08</v>
-      </c>
-      <c r="DI14" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="DJ14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="DK14" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="DL14" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="DM14" t="n">
-        <v>47.85</v>
-      </c>
-      <c r="DN14" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="DO14" t="n">
-        <v>2</v>
-      </c>
-      <c r="DP14" t="n">
-        <v>12.86</v>
-      </c>
-      <c r="DQ14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="DR14" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="DS14" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="DT14" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="DU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV14" t="n">
-        <v>48.55</v>
-      </c>
-      <c r="DW14" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="DX14" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="DY14" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="DZ14" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="EA14" t="n">
-        <v>20.33</v>
-      </c>
-      <c r="EB14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="EC14" t="n">
         <v>1.67</v>
       </c>
     </row>

--- a/data/teams/leagues/Averages_Finland_Veikkausliiga_2025.xlsx
+++ b/data/teams/leagues/Averages_Finland_Veikkausliiga_2025.xlsx
@@ -1424,7 +1424,7 @@
         <v>11.88</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.56</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
         <v>5.19</v>
@@ -1445,16 +1445,16 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>45.88</v>
+        <v>45.69</v>
       </c>
       <c r="Y2" t="n">
         <v>0.19</v>
       </c>
       <c r="Z2" t="n">
-        <v>12</v>
+        <v>11.88</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.81</v>
+        <v>7.69</v>
       </c>
       <c r="AB2" t="n">
         <v>4.19</v>
@@ -1736,7 +1736,7 @@
         <v>11.07</v>
       </c>
       <c r="DQ2" t="n">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="DR2" t="n">
         <v>6</v>
@@ -1751,16 +1751,16 @@
         <v>0.03</v>
       </c>
       <c r="DV2" t="n">
-        <v>45.19</v>
+        <v>45.1</v>
       </c>
       <c r="DW2" t="n">
         <v>0.19</v>
       </c>
       <c r="DX2" t="n">
-        <v>11.12</v>
+        <v>11.07</v>
       </c>
       <c r="DY2" t="n">
-        <v>6.75</v>
+        <v>6.69</v>
       </c>
       <c r="DZ2" t="n">
         <v>4.38</v>
@@ -1929,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>55.06</v>
+        <v>55.12</v>
       </c>
       <c r="AZ3" t="n">
         <v>0.06</v>
@@ -2150,7 +2150,7 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>57</v>
+        <v>57.03</v>
       </c>
       <c r="DW3" t="n">
         <v>0.03</v>
@@ -2646,7 +2646,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>54.81</v>
+        <v>54.75</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -2706,7 +2706,7 @@
         <v>8</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.31</v>
+        <v>2.19</v>
       </c>
       <c r="AS5" t="n">
         <v>3.56</v>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>55.19</v>
+        <v>55.38</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.12</v>
@@ -2937,7 +2937,7 @@
         <v>8.279999999999999</v>
       </c>
       <c r="DQ5" t="n">
-        <v>2.94</v>
+        <v>2.38</v>
       </c>
       <c r="DR5" t="n">
         <v>4.59</v>
@@ -2952,7 +2952,7 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55</v>
+        <v>55.06</v>
       </c>
       <c r="DW5" t="n">
         <v>0.06</v>
@@ -3112,7 +3112,7 @@
         <v>2.25</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.5</v>
+        <v>4.62</v>
       </c>
       <c r="AT6" t="n">
         <v>1.12</v>
@@ -3343,7 +3343,7 @@
         <v>2.18</v>
       </c>
       <c r="DR6" t="n">
-        <v>4.38</v>
+        <v>4.44</v>
       </c>
       <c r="DS6" t="n">
         <v>0.12</v>
@@ -3431,10 +3431,10 @@
         <v>13.29</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.21</v>
+        <v>2.86</v>
       </c>
       <c r="R7" t="n">
-        <v>6</v>
+        <v>5.86</v>
       </c>
       <c r="S7" t="n">
         <v>1.93</v>
@@ -3452,16 +3452,16 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>50.21</v>
+        <v>50.64</v>
       </c>
       <c r="Y7" t="n">
         <v>0.21</v>
       </c>
       <c r="Z7" t="n">
-        <v>11.36</v>
+        <v>11.07</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.29</v>
+        <v>7</v>
       </c>
       <c r="AB7" t="n">
         <v>4.07</v>
@@ -3470,7 +3470,7 @@
         <v>23.71</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE7" t="n">
         <v>1.57</v>
@@ -3743,10 +3743,10 @@
         <v>11.86</v>
       </c>
       <c r="DQ7" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.33</v>
+        <v>6.26</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
@@ -3758,16 +3758,16 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>46.15</v>
+        <v>46.37</v>
       </c>
       <c r="DW7" t="n">
         <v>0.11</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.59</v>
+        <v>10.44</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.41</v>
+        <v>6.26</v>
       </c>
       <c r="DZ7" t="n">
         <v>4.19</v>
@@ -3776,7 +3776,7 @@
         <v>21.26</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="EC7" t="n">
         <v>1.56</v>
@@ -4721,7 +4721,7 @@
         <v>9.92</v>
       </c>
       <c r="AR10" t="n">
-        <v>4</v>
+        <v>3.54</v>
       </c>
       <c r="AS10" t="n">
         <v>10.62</v>
@@ -4742,16 +4742,16 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>43.62</v>
+        <v>43.15</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.08</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.62</v>
+        <v>7.54</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.54</v>
+        <v>4.46</v>
       </c>
       <c r="BC10" t="n">
         <v>3.08</v>
@@ -4760,7 +4760,7 @@
         <v>20.46</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="BF10" t="n">
         <v>1.08</v>
@@ -4952,7 +4952,7 @@
         <v>9.26</v>
       </c>
       <c r="DQ10" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="DR10" t="n">
         <v>9.970000000000001</v>
@@ -4967,16 +4967,16 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>44.93</v>
+        <v>44.7</v>
       </c>
       <c r="DW10" t="n">
         <v>0.04</v>
       </c>
       <c r="DX10" t="n">
-        <v>8.779999999999999</v>
+        <v>8.74</v>
       </c>
       <c r="DY10" t="n">
-        <v>5.33</v>
+        <v>5.29</v>
       </c>
       <c r="DZ10" t="n">
         <v>3.45</v>
@@ -4985,7 +4985,7 @@
         <v>19.41</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="EC10" t="n">
         <v>1.23</v>
@@ -5449,7 +5449,7 @@
         <v>4.12</v>
       </c>
       <c r="R12" t="n">
-        <v>4.44</v>
+        <v>4.5</v>
       </c>
       <c r="S12" t="n">
         <v>1.12</v>
@@ -5757,7 +5757,7 @@
         <v>3.34</v>
       </c>
       <c r="DR12" t="n">
-        <v>4.85</v>
+        <v>4.88</v>
       </c>
       <c r="DS12" t="n">
         <v>0.12</v>

--- a/data/teams/leagues/Averages_Finland_Veikkausliiga_2025.xlsx
+++ b/data/teams/leagues/Averages_Finland_Veikkausliiga_2025.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -706,667 +694,667 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>total_games</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>home_games</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>away_games</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>home_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>home_avg_2h_cards</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>home_avg_2h_corners</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>home_avg_attacks</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>home_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>home_avg_cards_num</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>home_avg_corners</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>home_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>home_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>home_avg_fh_cards</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>home_avg_fh_corners</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>home_avg_fouls</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>home_avg_freekicks</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>home_avg_goalkicks</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>home_avg_goals_conceded</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>home_avg_goals_scored</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>home_avg_penalties_won</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>home_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>home_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>home_avg_possession</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>home_avg_red_cards</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>home_avg_shots</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>home_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>home_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>home_avg_throwins</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>home_avg_xg</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>home_avg_yellow_cards</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>away_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>away_avg_2h_cards</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>away_avg_2h_corners</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>away_avg_attacks</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>away_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>away_avg_cards_num</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>away_avg_corners</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>away_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>away_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>away_avg_fh_cards</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>away_avg_fh_corners</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>away_avg_fouls</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>away_avg_freekicks</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>away_avg_goalkicks</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>away_avg_goals_conceded</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>away_avg_goals_scored</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>away_avg_penalties_won</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>away_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>away_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>away_avg_possession</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>away_avg_red_cards</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>away_avg_shots</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>away_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>away_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>away_avg_throwins</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>away_avg_xg</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>away_avg_yellow_cards</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>totalGoalCount</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>totalCornerCount</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>overallGoalCount</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>ht_goals_team_a</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>ht_goals_team_b</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>goals_2hg_team_a</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>goals_2hg_team_b</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>GoalCount_2hg</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>HTGoalCount</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>corner_fh_count</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>corner_2h_count</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>over05</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>over15</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>over25</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>over35</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>over45</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>over55</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>btts</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>avg_odds_ft_1</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_1_odd</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>avg_odds_ft_x</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_x_odd</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>avg_odds_ft_2</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_2_odd</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_over05</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_over15</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_under05</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_under15</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>avg_odds_btts_no</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>avg_odds_btts_yes</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>avg_odds_corners_over_85</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>avg_odds_corners_over_95</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>avg_odds_corners_under_85</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>avg_odds_corners_under_95</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over15</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over25</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over35</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_over05_odd</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_over15_odd</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_under05_odd</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_under15_odd</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>avg_pinnacle_btts_no_odd</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>avg_pinnacle_btts_yes_odd</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_85_odd</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_95_odd</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_85_odd</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_95_odd</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over15_odd</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over25_odd</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over35_odd</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>total_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>total_avg_2h_cards</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>total_avg_2h_corners</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>total_avg_attacks</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>total_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>total_avg_cards_num</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>total_avg_corners</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>total_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>total_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>total_avg_fh_cards</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>total_avg_fh_corners</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>total_avg_fouls</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>total_avg_freekicks</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>total_avg_goalkicks</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>total_avg_penalties_won</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>total_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>total_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>total_avg_possession</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>total_avg_red_cards</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>total_avg_shots</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>total_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>total_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>total_avg_throwins</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>total_avg_xg</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>total_avg_yellow_cards</t>
         </is>
